--- a/RL/results_scalar_film_b.xlsx
+++ b/RL/results_scalar_film_b.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,112 +418,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Expression #</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Expression Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Is Feasible</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Initial Exec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Initial Keys</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Initial Noise</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Agent Final Exec</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Agent Final Keys</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Agent Final Noise</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Agent Cost Reduction (%)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Agent Violated</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Safe Final Exec</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Safe Final Keys</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Safe Final Noise</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Safe Cost Reduction (%)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Safe Violated</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Safety Activated</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Best Valid Step</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Total Steps</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>RL Time (ms)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Noise Margin</t>
         </is>
@@ -605,7 +593,7 @@
         <v>75</v>
       </c>
       <c r="U2" t="n">
-        <v>19354.6</v>
+        <v>17561.6</v>
       </c>
       <c r="V2" t="n">
         <v>93.29000000000001</v>
@@ -675,7 +663,7 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>1163.6</v>
+        <v>4532.7</v>
       </c>
       <c r="V3" t="n">
         <v>232.81</v>
@@ -745,7 +733,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>289.1</v>
+        <v>287</v>
       </c>
       <c r="V4" t="n">
         <v>200.63</v>
@@ -815,7 +803,7 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>575.3</v>
+        <v>568</v>
       </c>
       <c r="V5" t="n">
         <v>200.63</v>
@@ -885,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>174.8</v>
+        <v>171.2</v>
       </c>
       <c r="V6" t="n">
         <v>164.85</v>
@@ -955,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>244</v>
+        <v>188.6</v>
       </c>
       <c r="V7" t="n">
         <v>163.65</v>
@@ -1025,7 +1013,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>610.8</v>
+        <v>739.6</v>
       </c>
       <c r="V8" t="n">
         <v>162.45</v>
@@ -1095,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>251.5</v>
+        <v>577.3</v>
       </c>
       <c r="V9" t="n">
         <v>164.85</v>
@@ -1165,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>836.9</v>
+        <v>1050.3</v>
       </c>
       <c r="V10" t="n">
         <v>164.85</v>
@@ -1235,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>155</v>
+        <v>128.4</v>
       </c>
       <c r="V11" t="n">
         <v>199.43</v>
@@ -1305,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>224.6</v>
+        <v>178.8</v>
       </c>
       <c r="V12" t="n">
         <v>198.23</v>
@@ -1375,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>849.5</v>
+        <v>470.9</v>
       </c>
       <c r="V13" t="n">
         <v>197.03</v>
@@ -1445,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>164</v>
+        <v>100.4</v>
       </c>
       <c r="V14" t="n">
         <v>200.63</v>
@@ -1515,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>246.9</v>
+        <v>110</v>
       </c>
       <c r="V15" t="n">
         <v>199.43</v>
@@ -1585,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>455.4</v>
+        <v>217.8</v>
       </c>
       <c r="V16" t="n">
         <v>198.23</v>
@@ -1655,7 +1643,7 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>633.6</v>
+        <v>342</v>
       </c>
       <c r="V17" t="n">
         <v>199.43</v>
@@ -1725,7 +1713,7 @@
         <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1744.4</v>
+        <v>1133.2</v>
       </c>
       <c r="V18" t="n">
         <v>164.85</v>
@@ -1795,7 +1783,7 @@
         <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1188.5</v>
+        <v>748.1</v>
       </c>
       <c r="V19" t="n">
         <v>200.63</v>
@@ -1865,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>244.7</v>
+        <v>153.8</v>
       </c>
       <c r="V20" t="n">
         <v>129.07</v>
@@ -1935,7 +1923,7 @@
         <v>75</v>
       </c>
       <c r="U21" t="n">
-        <v>31736.9</v>
+        <v>20849.3</v>
       </c>
       <c r="V21" t="n">
         <v>21.73</v>
@@ -2005,7 +1993,7 @@
         <v>75</v>
       </c>
       <c r="U22" t="n">
-        <v>20867.3</v>
+        <v>13444.9</v>
       </c>
       <c r="V22" t="n">
         <v>57.51</v>
@@ -2075,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>349.2</v>
+        <v>186.6</v>
       </c>
       <c r="V23" t="n">
         <v>98.08</v>
@@ -2145,7 +2133,7 @@
         <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>986.8</v>
+        <v>473.5</v>
       </c>
       <c r="V24" t="n">
         <v>232.81</v>
@@ -2215,7 +2203,7 @@
         <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>1985</v>
+        <v>1175.1</v>
       </c>
       <c r="V25" t="n">
         <v>232.81</v>
@@ -2285,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>401.6</v>
+        <v>206.7</v>
       </c>
       <c r="V26" t="n">
         <v>200.63</v>
@@ -2355,7 +2343,7 @@
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>964.2</v>
+        <v>503.1</v>
       </c>
       <c r="V27" t="n">
         <v>200.63</v>
@@ -2425,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>383.9</v>
+        <v>138.9</v>
       </c>
       <c r="V28" t="n">
         <v>164.85</v>
@@ -2495,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>422</v>
+        <v>247</v>
       </c>
       <c r="V29" t="n">
         <v>163.65</v>
@@ -2565,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>927.1</v>
+        <v>576</v>
       </c>
       <c r="V30" t="n">
         <v>161.25</v>
@@ -2635,7 +2623,7 @@
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>762.1</v>
+        <v>348.9</v>
       </c>
       <c r="V31" t="n">
         <v>164.85</v>
@@ -2705,7 +2693,7 @@
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1824.9</v>
+        <v>1179.4</v>
       </c>
       <c r="V32" t="n">
         <v>164.85</v>
@@ -2775,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>240</v>
+        <v>128.4</v>
       </c>
       <c r="V33" t="n">
         <v>199.43</v>
@@ -2845,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>483.9</v>
+        <v>223.3</v>
       </c>
       <c r="V34" t="n">
         <v>198.23</v>
@@ -2915,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>731.9</v>
+        <v>421.1</v>
       </c>
       <c r="V35" t="n">
         <v>195.84</v>
@@ -2985,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>186</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="V36" t="n">
         <v>200.63</v>
@@ -3055,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>299.7</v>
+        <v>141</v>
       </c>
       <c r="V37" t="n">
         <v>199.43</v>
@@ -3125,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>466.2</v>
+        <v>289</v>
       </c>
       <c r="V38" t="n">
         <v>197.03</v>
@@ -3195,7 +3183,7 @@
         <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>1035.3</v>
+        <v>573.8</v>
       </c>
       <c r="V39" t="n">
         <v>199.43</v>
@@ -3265,7 +3253,7 @@
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>994.4</v>
+        <v>579.9</v>
       </c>
       <c r="V40" t="n">
         <v>200.63</v>
@@ -3335,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>224.2</v>
+        <v>133.8</v>
       </c>
       <c r="V41" t="n">
         <v>164.85</v>
@@ -3405,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>418.5</v>
+        <v>246</v>
       </c>
       <c r="V42" t="n">
         <v>129.07</v>
@@ -3475,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>278.5</v>
+        <v>123.8</v>
       </c>
       <c r="V43" t="n">
         <v>166.05</v>
@@ -3545,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>373.5</v>
+        <v>262.5</v>
       </c>
       <c r="V44" t="n">
         <v>131.47</v>
@@ -3615,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>515.4</v>
+        <v>270.7</v>
       </c>
       <c r="V45" t="n">
         <v>153.29</v>
@@ -3685,7 +3673,7 @@
         <v>4</v>
       </c>
       <c r="U46" t="n">
-        <v>1870.7</v>
+        <v>984.2</v>
       </c>
       <c r="V46" t="n">
         <v>292.81</v>
@@ -3755,7 +3743,7 @@
         <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>386.9</v>
+        <v>178.3</v>
       </c>
       <c r="V47" t="n">
         <v>260.63</v>
@@ -3825,7 +3813,7 @@
         <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>903.4</v>
+        <v>502.8</v>
       </c>
       <c r="V48" t="n">
         <v>260.63</v>
@@ -3895,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>235.4</v>
+        <v>127.7</v>
       </c>
       <c r="V49" t="n">
         <v>224.85</v>
@@ -3965,7 +3953,7 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>435.9</v>
+        <v>186</v>
       </c>
       <c r="V50" t="n">
         <v>223.65</v>
@@ -4035,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>686.1</v>
+        <v>493.5</v>
       </c>
       <c r="V51" t="n">
         <v>222.45</v>
@@ -4105,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>350.3</v>
+        <v>169.5</v>
       </c>
       <c r="V52" t="n">
         <v>224.85</v>
@@ -4175,7 +4163,7 @@
         <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>1128.2</v>
+        <v>662.2</v>
       </c>
       <c r="V53" t="n">
         <v>224.85</v>
@@ -4245,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>234.6</v>
+        <v>113</v>
       </c>
       <c r="V54" t="n">
         <v>259.43</v>
@@ -4315,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>331.2</v>
+        <v>145.1</v>
       </c>
       <c r="V55" t="n">
         <v>258.23</v>
@@ -4385,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>720.1</v>
+        <v>368</v>
       </c>
       <c r="V56" t="n">
         <v>257.03</v>
@@ -4455,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>152.8</v>
+        <v>101.1</v>
       </c>
       <c r="V57" t="n">
         <v>260.63</v>
@@ -4525,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>276.3</v>
+        <v>111.1</v>
       </c>
       <c r="V58" t="n">
         <v>259.43</v>
@@ -4595,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>438.8</v>
+        <v>223.9</v>
       </c>
       <c r="V59" t="n">
         <v>258.23</v>
@@ -4665,7 +4653,7 @@
         <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>849.2</v>
+        <v>439.2</v>
       </c>
       <c r="V60" t="n">
         <v>224.85</v>
@@ -4735,7 +4723,7 @@
         <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>1294.4</v>
+        <v>738</v>
       </c>
       <c r="V61" t="n">
         <v>259.43</v>
@@ -4805,7 +4793,7 @@
         <v>4</v>
       </c>
       <c r="U62" t="n">
-        <v>1748.5</v>
+        <v>926.5</v>
       </c>
       <c r="V62" t="n">
         <v>260.63</v>
@@ -4875,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>309.4</v>
+        <v>156.6</v>
       </c>
       <c r="V63" t="n">
         <v>189.07</v>
@@ -4945,7 +4933,7 @@
         <v>75</v>
       </c>
       <c r="U64" t="n">
-        <v>84494.7</v>
+        <v>52031.9</v>
       </c>
       <c r="V64" t="n">
         <v>80.53</v>
@@ -5015,7 +5003,7 @@
         <v>5</v>
       </c>
       <c r="U65" t="n">
-        <v>3912.5</v>
+        <v>2432.8</v>
       </c>
       <c r="V65" t="n">
         <v>113.92</v>
@@ -5085,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>429.9</v>
+        <v>255.6</v>
       </c>
       <c r="V66" t="n">
         <v>158.08</v>
@@ -5155,7 +5143,7 @@
         <v>3</v>
       </c>
       <c r="U67" t="n">
-        <v>782.7</v>
+        <v>464.9</v>
       </c>
       <c r="V67" t="n">
         <v>292.81</v>
@@ -5225,7 +5213,7 @@
         <v>4</v>
       </c>
       <c r="U68" t="n">
-        <v>2243.9</v>
+        <v>1197.7</v>
       </c>
       <c r="V68" t="n">
         <v>292.81</v>
@@ -5295,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>364.1</v>
+        <v>194.2</v>
       </c>
       <c r="V69" t="n">
         <v>260.63</v>
@@ -5365,7 +5353,7 @@
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>936.2</v>
+        <v>514</v>
       </c>
       <c r="V70" t="n">
         <v>260.63</v>
@@ -5435,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>407.3</v>
+        <v>257.7</v>
       </c>
       <c r="V71" t="n">
         <v>224.85</v>
@@ -5505,7 +5493,7 @@
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>522</v>
+        <v>232.7</v>
       </c>
       <c r="V72" t="n">
         <v>223.65</v>
@@ -5575,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>1017.9</v>
+        <v>532.7</v>
       </c>
       <c r="V73" t="n">
         <v>221.25</v>
@@ -5645,7 +5633,7 @@
         <v>3</v>
       </c>
       <c r="U74" t="n">
-        <v>868.6</v>
+        <v>411.9</v>
       </c>
       <c r="V74" t="n">
         <v>224.85</v>
@@ -5715,7 +5703,7 @@
         <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>1460.6</v>
+        <v>872.7</v>
       </c>
       <c r="V75" t="n">
         <v>224.85</v>
@@ -5785,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>272.4</v>
+        <v>123.7</v>
       </c>
       <c r="V76" t="n">
         <v>259.43</v>
@@ -5855,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>411.7</v>
+        <v>204.8</v>
       </c>
       <c r="V77" t="n">
         <v>258.23</v>
@@ -5925,7 +5913,7 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>703.1</v>
+        <v>412.7</v>
       </c>
       <c r="V78" t="n">
         <v>255.84</v>
@@ -5995,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>175.6</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="V79" t="n">
         <v>260.63</v>
@@ -6065,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>229.2</v>
+        <v>129.2</v>
       </c>
       <c r="V80" t="n">
         <v>259.43</v>
@@ -6135,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>562.8</v>
+        <v>260.3</v>
       </c>
       <c r="V81" t="n">
         <v>257.03</v>
@@ -6205,7 +6193,7 @@
         <v>2</v>
       </c>
       <c r="U82" t="n">
-        <v>1159.5</v>
+        <v>550</v>
       </c>
       <c r="V82" t="n">
         <v>259.43</v>
@@ -6275,7 +6263,7 @@
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>1089.3</v>
+        <v>475.8</v>
       </c>
       <c r="V83" t="n">
         <v>260.63</v>
@@ -6345,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>323.2</v>
+        <v>121.2</v>
       </c>
       <c r="V84" t="n">
         <v>224.85</v>
@@ -6415,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>568.6</v>
+        <v>246</v>
       </c>
       <c r="V85" t="n">
         <v>189.07</v>
@@ -6485,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>233.5</v>
+        <v>104.9</v>
       </c>
       <c r="V86" t="n">
         <v>226.05</v>
@@ -6555,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>445</v>
+        <v>163.1</v>
       </c>
       <c r="V87" t="n">
         <v>191.47</v>
@@ -6625,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>658</v>
+        <v>256.3</v>
       </c>
       <c r="V88" t="n">
         <v>999853.29</v>
@@ -6695,7 +6683,7 @@
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>1858.1</v>
+        <v>720.6</v>
       </c>
       <c r="V89" t="n">
         <v>999992.8100000001</v>
@@ -6765,7 +6753,7 @@
         <v>1</v>
       </c>
       <c r="U90" t="n">
-        <v>331.1</v>
+        <v>118.5</v>
       </c>
       <c r="V90" t="n">
         <v>999960.63</v>
@@ -6835,7 +6823,7 @@
         <v>3</v>
       </c>
       <c r="U91" t="n">
-        <v>1670.1</v>
+        <v>454.5</v>
       </c>
       <c r="V91" t="n">
         <v>999960.63</v>
@@ -6905,7 +6893,7 @@
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>480.6</v>
+        <v>120.8</v>
       </c>
       <c r="V92" t="n">
         <v>999924.85</v>
@@ -6975,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>381.9</v>
+        <v>160.3</v>
       </c>
       <c r="V93" t="n">
         <v>999923.65</v>
@@ -7045,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>1469.9</v>
+        <v>489</v>
       </c>
       <c r="V94" t="n">
         <v>999922.45</v>
@@ -7115,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>518.1</v>
+        <v>157.1</v>
       </c>
       <c r="V95" t="n">
         <v>999924.85</v>
@@ -7185,7 +7173,7 @@
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>1505</v>
+        <v>627.6</v>
       </c>
       <c r="V96" t="n">
         <v>999924.85</v>
@@ -7255,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>318.5</v>
+        <v>103.9</v>
       </c>
       <c r="V97" t="n">
         <v>999959.4300000001</v>
@@ -7325,7 +7313,7 @@
         <v>1</v>
       </c>
       <c r="U98" t="n">
-        <v>442.3</v>
+        <v>142.7</v>
       </c>
       <c r="V98" t="n">
         <v>999958.23</v>
@@ -7395,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="U99" t="n">
-        <v>706.6</v>
+        <v>363.6</v>
       </c>
       <c r="V99" t="n">
         <v>999957.03</v>
@@ -7465,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>195.7</v>
+        <v>90.3</v>
       </c>
       <c r="V100" t="n">
         <v>999960.63</v>
@@ -7535,7 +7523,7 @@
         <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>299.7</v>
+        <v>104.3</v>
       </c>
       <c r="V101" t="n">
         <v>999959.4300000001</v>
@@ -7605,7 +7593,7 @@
         <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>416.8</v>
+        <v>209.3</v>
       </c>
       <c r="V102" t="n">
         <v>999958.23</v>
@@ -7675,7 +7663,7 @@
         <v>3</v>
       </c>
       <c r="U103" t="n">
-        <v>1007.3</v>
+        <v>412.2</v>
       </c>
       <c r="V103" t="n">
         <v>999924.85</v>
@@ -7745,7 +7733,7 @@
         <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>1880.4</v>
+        <v>981.5</v>
       </c>
       <c r="V104" t="n">
         <v>999924.85</v>
@@ -7815,7 +7803,7 @@
         <v>4</v>
       </c>
       <c r="U105" t="n">
-        <v>1768.8</v>
+        <v>890.2</v>
       </c>
       <c r="V105" t="n">
         <v>999960.63</v>
@@ -7885,7 +7873,7 @@
         <v>1</v>
       </c>
       <c r="U106" t="n">
-        <v>355.9</v>
+        <v>168.7</v>
       </c>
       <c r="V106" t="n">
         <v>999889.0699999999</v>
@@ -7955,7 +7943,7 @@
         <v>75</v>
       </c>
       <c r="U107" t="n">
-        <v>37476.7</v>
+        <v>26180.7</v>
       </c>
       <c r="V107" t="n">
         <v>999781.73</v>
@@ -8025,7 +8013,7 @@
         <v>5</v>
       </c>
       <c r="U108" t="n">
-        <v>3797.5</v>
+        <v>1941</v>
       </c>
       <c r="V108" t="n">
         <v>999813.92</v>
@@ -8095,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="U109" t="n">
-        <v>345.7</v>
+        <v>217.3</v>
       </c>
       <c r="V109" t="n">
         <v>999858.08</v>
@@ -8165,7 +8153,7 @@
         <v>3</v>
       </c>
       <c r="U110" t="n">
-        <v>819.9</v>
+        <v>517.6</v>
       </c>
       <c r="V110" t="n">
         <v>999992.8100000001</v>
@@ -8235,7 +8223,7 @@
         <v>4</v>
       </c>
       <c r="U111" t="n">
-        <v>2248.3</v>
+        <v>1114</v>
       </c>
       <c r="V111" t="n">
         <v>999992.8100000001</v>
@@ -8305,7 +8293,7 @@
         <v>2</v>
       </c>
       <c r="U112" t="n">
-        <v>517.5</v>
+        <v>263.4</v>
       </c>
       <c r="V112" t="n">
         <v>999960.63</v>
@@ -8375,7 +8363,7 @@
         <v>2</v>
       </c>
       <c r="U113" t="n">
-        <v>952.6</v>
+        <v>525.5</v>
       </c>
       <c r="V113" t="n">
         <v>999960.63</v>
@@ -8445,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="U114" t="n">
-        <v>270.5</v>
+        <v>144.6</v>
       </c>
       <c r="V114" t="n">
         <v>999924.85</v>
@@ -8515,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>454.3</v>
+        <v>266.6</v>
       </c>
       <c r="V115" t="n">
         <v>999923.65</v>
@@ -8585,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="U116" t="n">
-        <v>1012.6</v>
+        <v>718.6</v>
       </c>
       <c r="V116" t="n">
         <v>999921.25</v>
@@ -8655,7 +8643,7 @@
         <v>2</v>
       </c>
       <c r="U117" t="n">
-        <v>911.6</v>
+        <v>357.4</v>
       </c>
       <c r="V117" t="n">
         <v>999924.85</v>
@@ -8725,7 +8713,7 @@
         <v>2</v>
       </c>
       <c r="U118" t="n">
-        <v>1373.4</v>
+        <v>1029.4</v>
       </c>
       <c r="V118" t="n">
         <v>999924.85</v>
@@ -8795,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>255.7</v>
+        <v>133.8</v>
       </c>
       <c r="V119" t="n">
         <v>999959.4300000001</v>
@@ -8865,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="U120" t="n">
-        <v>423.6</v>
+        <v>227.9</v>
       </c>
       <c r="V120" t="n">
         <v>999958.23</v>
@@ -8935,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="U121" t="n">
-        <v>820.3</v>
+        <v>411.1</v>
       </c>
       <c r="V121" t="n">
         <v>999955.84</v>
@@ -9005,7 +8993,7 @@
         <v>1</v>
       </c>
       <c r="U122" t="n">
-        <v>174.5</v>
+        <v>92.3</v>
       </c>
       <c r="V122" t="n">
         <v>999960.63</v>
@@ -9075,7 +9063,7 @@
         <v>1</v>
       </c>
       <c r="U123" t="n">
-        <v>250.7</v>
+        <v>142.7</v>
       </c>
       <c r="V123" t="n">
         <v>999959.4300000001</v>
@@ -9145,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="U124" t="n">
-        <v>442.2</v>
+        <v>291</v>
       </c>
       <c r="V124" t="n">
         <v>999957.03</v>
@@ -9215,7 +9203,7 @@
         <v>2</v>
       </c>
       <c r="U125" t="n">
-        <v>998.6</v>
+        <v>590.2</v>
       </c>
       <c r="V125" t="n">
         <v>999959.4300000001</v>
@@ -9285,7 +9273,7 @@
         <v>3</v>
       </c>
       <c r="U126" t="n">
-        <v>882</v>
+        <v>581</v>
       </c>
       <c r="V126" t="n">
         <v>999960.63</v>
@@ -9355,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="U127" t="n">
-        <v>233.7</v>
+        <v>161.9</v>
       </c>
       <c r="V127" t="n">
         <v>999924.85</v>
@@ -9425,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="U128" t="n">
-        <v>425.9</v>
+        <v>396.6</v>
       </c>
       <c r="V128" t="n">
         <v>999889.0699999999</v>
@@ -9495,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="U129" t="n">
-        <v>223</v>
+        <v>267.2</v>
       </c>
       <c r="V129" t="n">
         <v>999926.05</v>
@@ -9565,7 +9553,7 @@
         <v>1</v>
       </c>
       <c r="U130" t="n">
-        <v>313.3</v>
+        <v>749.1</v>
       </c>
       <c r="V130" t="n">
         <v>999891.47</v>
@@ -9586,42 +9574,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Budget</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Feasible Expressions</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Agent Avg Cost Red (%)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Agent Violation Rate (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Safe Avg Cost Red (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Safe Violation Rate (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Safety Activations</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Avg Safe Noise Margin</t>
         </is>

--- a/RL/results_scalar_film_b.xlsx
+++ b/RL/results_scalar_film_b.xlsx
@@ -593,7 +593,7 @@
         <v>75</v>
       </c>
       <c r="U2" t="n">
-        <v>17561.6</v>
+        <v>12333.2</v>
       </c>
       <c r="V2" t="n">
         <v>93.29000000000001</v>
@@ -663,7 +663,7 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>4532.7</v>
+        <v>754.2</v>
       </c>
       <c r="V3" t="n">
         <v>232.81</v>
@@ -733,7 +733,7 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>287</v>
+        <v>160.2</v>
       </c>
       <c r="V4" t="n">
         <v>200.63</v>
@@ -803,7 +803,7 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>568</v>
+        <v>365.7</v>
       </c>
       <c r="V5" t="n">
         <v>200.63</v>
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>171.2</v>
+        <v>112.1</v>
       </c>
       <c r="V6" t="n">
         <v>164.85</v>
@@ -943,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>188.6</v>
+        <v>150.3</v>
       </c>
       <c r="V7" t="n">
         <v>163.65</v>
@@ -1013,7 +1013,7 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>739.6</v>
+        <v>425</v>
       </c>
       <c r="V8" t="n">
         <v>162.45</v>
@@ -1083,7 +1083,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>577.3</v>
+        <v>137.8</v>
       </c>
       <c r="V9" t="n">
         <v>164.85</v>
@@ -1153,7 +1153,7 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1050.3</v>
+        <v>544.4</v>
       </c>
       <c r="V10" t="n">
         <v>164.85</v>
@@ -1223,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>128.4</v>
+        <v>115.8</v>
       </c>
       <c r="V11" t="n">
         <v>199.43</v>
@@ -1293,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>178.8</v>
+        <v>156.5</v>
       </c>
       <c r="V12" t="n">
         <v>198.23</v>
@@ -1363,7 +1363,7 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>470.9</v>
+        <v>321.6</v>
       </c>
       <c r="V13" t="n">
         <v>197.03</v>
@@ -1433,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>100.4</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>200.63</v>
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>110</v>
+        <v>90.3</v>
       </c>
       <c r="V15" t="n">
         <v>199.43</v>
@@ -1573,7 +1573,7 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>217.8</v>
+        <v>185.9</v>
       </c>
       <c r="V16" t="n">
         <v>198.23</v>
@@ -1643,7 +1643,7 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>342</v>
+        <v>296</v>
       </c>
       <c r="V17" t="n">
         <v>199.43</v>
@@ -1713,7 +1713,7 @@
         <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1133.2</v>
+        <v>872.2</v>
       </c>
       <c r="V18" t="n">
         <v>164.85</v>
@@ -1783,7 +1783,7 @@
         <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>748.1</v>
+        <v>664.6</v>
       </c>
       <c r="V19" t="n">
         <v>200.63</v>
@@ -1853,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>153.8</v>
+        <v>143</v>
       </c>
       <c r="V20" t="n">
         <v>129.07</v>
@@ -1923,7 +1923,7 @@
         <v>75</v>
       </c>
       <c r="U21" t="n">
-        <v>20849.3</v>
+        <v>17887.6</v>
       </c>
       <c r="V21" t="n">
         <v>21.73</v>
@@ -1993,7 +1993,7 @@
         <v>75</v>
       </c>
       <c r="U22" t="n">
-        <v>13444.9</v>
+        <v>13024.8</v>
       </c>
       <c r="V22" t="n">
         <v>57.51</v>
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>186.6</v>
+        <v>231.1</v>
       </c>
       <c r="V23" t="n">
         <v>98.08</v>
@@ -2133,7 +2133,7 @@
         <v>4</v>
       </c>
       <c r="U24" t="n">
-        <v>473.5</v>
+        <v>545.2</v>
       </c>
       <c r="V24" t="n">
         <v>232.81</v>
@@ -2203,7 +2203,7 @@
         <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>1175.1</v>
+        <v>1110.5</v>
       </c>
       <c r="V25" t="n">
         <v>232.81</v>
@@ -2273,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>206.7</v>
+        <v>191.3</v>
       </c>
       <c r="V26" t="n">
         <v>200.63</v>
@@ -2343,7 +2343,7 @@
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>503.1</v>
+        <v>508.5</v>
       </c>
       <c r="V27" t="n">
         <v>200.63</v>
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>138.9</v>
+        <v>139.6</v>
       </c>
       <c r="V28" t="n">
         <v>164.85</v>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>247</v>
+        <v>245.1</v>
       </c>
       <c r="V29" t="n">
         <v>163.65</v>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>576</v>
+        <v>577.7</v>
       </c>
       <c r="V30" t="n">
         <v>161.25</v>
@@ -2623,7 +2623,7 @@
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>348.9</v>
+        <v>385.9</v>
       </c>
       <c r="V31" t="n">
         <v>164.85</v>
@@ -2693,7 +2693,7 @@
         <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1179.4</v>
+        <v>1077.5</v>
       </c>
       <c r="V32" t="n">
         <v>164.85</v>
@@ -2763,7 +2763,7 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>128.4</v>
+        <v>206.8</v>
       </c>
       <c r="V33" t="n">
         <v>199.43</v>
@@ -2833,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>223.3</v>
+        <v>223.8</v>
       </c>
       <c r="V34" t="n">
         <v>198.23</v>
@@ -2903,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>421.1</v>
+        <v>403.9</v>
       </c>
       <c r="V35" t="n">
         <v>195.84</v>
@@ -2973,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>88.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="V36" t="n">
         <v>200.63</v>
@@ -3043,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>141</v>
+        <v>135.6</v>
       </c>
       <c r="V37" t="n">
         <v>199.43</v>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>289</v>
+        <v>274.8</v>
       </c>
       <c r="V38" t="n">
         <v>197.03</v>
@@ -3183,7 +3183,7 @@
         <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>573.8</v>
+        <v>551.1</v>
       </c>
       <c r="V39" t="n">
         <v>199.43</v>
@@ -3253,7 +3253,7 @@
         <v>3</v>
       </c>
       <c r="U40" t="n">
-        <v>579.9</v>
+        <v>466.6</v>
       </c>
       <c r="V40" t="n">
         <v>200.63</v>
@@ -3323,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>133.8</v>
+        <v>124</v>
       </c>
       <c r="V41" t="n">
         <v>164.85</v>
@@ -3393,7 +3393,7 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>246</v>
+        <v>235.6</v>
       </c>
       <c r="V42" t="n">
         <v>129.07</v>
@@ -3463,7 +3463,7 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>123.8</v>
+        <v>113.3</v>
       </c>
       <c r="V43" t="n">
         <v>166.05</v>
@@ -3533,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>262.5</v>
+        <v>177.1</v>
       </c>
       <c r="V44" t="n">
         <v>131.47</v>
@@ -3603,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>270.7</v>
+        <v>268.5</v>
       </c>
       <c r="V45" t="n">
         <v>153.29</v>
@@ -3673,7 +3673,7 @@
         <v>4</v>
       </c>
       <c r="U46" t="n">
-        <v>984.2</v>
+        <v>938.2</v>
       </c>
       <c r="V46" t="n">
         <v>292.81</v>
@@ -3743,7 +3743,7 @@
         <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>178.3</v>
+        <v>177</v>
       </c>
       <c r="V47" t="n">
         <v>260.63</v>
@@ -3813,7 +3813,7 @@
         <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>502.8</v>
+        <v>488</v>
       </c>
       <c r="V48" t="n">
         <v>260.63</v>
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>127.7</v>
+        <v>122.8</v>
       </c>
       <c r="V49" t="n">
         <v>224.85</v>
@@ -3953,7 +3953,7 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="V50" t="n">
         <v>223.65</v>
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>493.5</v>
+        <v>461.4</v>
       </c>
       <c r="V51" t="n">
         <v>222.45</v>
@@ -4093,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>169.5</v>
+        <v>150.8</v>
       </c>
       <c r="V52" t="n">
         <v>224.85</v>
@@ -4163,7 +4163,7 @@
         <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>662.2</v>
+        <v>612.3</v>
       </c>
       <c r="V53" t="n">
         <v>224.85</v>
@@ -4233,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>113</v>
+        <v>114.5</v>
       </c>
       <c r="V54" t="n">
         <v>259.43</v>
@@ -4303,7 +4303,7 @@
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>145.1</v>
+        <v>146.5</v>
       </c>
       <c r="V55" t="n">
         <v>258.23</v>
@@ -4373,7 +4373,7 @@
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>368</v>
+        <v>353.2</v>
       </c>
       <c r="V56" t="n">
         <v>257.03</v>
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>101.1</v>
+        <v>86.7</v>
       </c>
       <c r="V57" t="n">
         <v>260.63</v>
@@ -4513,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>111.1</v>
+        <v>103.4</v>
       </c>
       <c r="V58" t="n">
         <v>259.43</v>
@@ -4583,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>223.9</v>
+        <v>222.5</v>
       </c>
       <c r="V59" t="n">
         <v>258.23</v>
@@ -4653,7 +4653,7 @@
         <v>3</v>
       </c>
       <c r="U60" t="n">
-        <v>439.2</v>
+        <v>446.3</v>
       </c>
       <c r="V60" t="n">
         <v>224.85</v>
@@ -4723,7 +4723,7 @@
         <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>738</v>
+        <v>707.2</v>
       </c>
       <c r="V61" t="n">
         <v>259.43</v>
@@ -4793,7 +4793,7 @@
         <v>4</v>
       </c>
       <c r="U62" t="n">
-        <v>926.5</v>
+        <v>910.6</v>
       </c>
       <c r="V62" t="n">
         <v>260.63</v>
@@ -4863,7 +4863,7 @@
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>156.6</v>
+        <v>164.1</v>
       </c>
       <c r="V63" t="n">
         <v>189.07</v>
@@ -4933,7 +4933,7 @@
         <v>75</v>
       </c>
       <c r="U64" t="n">
-        <v>52031.9</v>
+        <v>57641.7</v>
       </c>
       <c r="V64" t="n">
         <v>80.53</v>
@@ -5003,7 +5003,7 @@
         <v>5</v>
       </c>
       <c r="U65" t="n">
-        <v>2432.8</v>
+        <v>2125.6</v>
       </c>
       <c r="V65" t="n">
         <v>113.92</v>
@@ -5073,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>255.6</v>
+        <v>250.4</v>
       </c>
       <c r="V66" t="n">
         <v>158.08</v>
@@ -5143,7 +5143,7 @@
         <v>3</v>
       </c>
       <c r="U67" t="n">
-        <v>464.9</v>
+        <v>523.4</v>
       </c>
       <c r="V67" t="n">
         <v>292.81</v>
@@ -5213,7 +5213,7 @@
         <v>4</v>
       </c>
       <c r="U68" t="n">
-        <v>1197.7</v>
+        <v>1228.4</v>
       </c>
       <c r="V68" t="n">
         <v>292.81</v>
@@ -5283,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>194.2</v>
+        <v>217.5</v>
       </c>
       <c r="V69" t="n">
         <v>260.63</v>
@@ -5353,7 +5353,7 @@
         <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>514</v>
+        <v>561.8</v>
       </c>
       <c r="V70" t="n">
         <v>260.63</v>
@@ -5423,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>257.7</v>
+        <v>274.9</v>
       </c>
       <c r="V71" t="n">
         <v>224.85</v>
@@ -5493,7 +5493,7 @@
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>232.7</v>
+        <v>273.7</v>
       </c>
       <c r="V72" t="n">
         <v>223.65</v>
@@ -5563,7 +5563,7 @@
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>532.7</v>
+        <v>574.5</v>
       </c>
       <c r="V73" t="n">
         <v>221.25</v>
@@ -5633,7 +5633,7 @@
         <v>3</v>
       </c>
       <c r="U74" t="n">
-        <v>411.9</v>
+        <v>499.6</v>
       </c>
       <c r="V74" t="n">
         <v>224.85</v>
@@ -5703,7 +5703,7 @@
         <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>872.7</v>
+        <v>927.8</v>
       </c>
       <c r="V75" t="n">
         <v>224.85</v>
@@ -5773,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>123.7</v>
+        <v>146</v>
       </c>
       <c r="V76" t="n">
         <v>259.43</v>
@@ -5843,7 +5843,7 @@
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>204.8</v>
+        <v>255.7</v>
       </c>
       <c r="V77" t="n">
         <v>258.23</v>
@@ -5913,7 +5913,7 @@
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>412.7</v>
+        <v>455</v>
       </c>
       <c r="V78" t="n">
         <v>255.84</v>
@@ -5983,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>89.09999999999999</v>
+        <v>110.5</v>
       </c>
       <c r="V79" t="n">
         <v>260.63</v>
@@ -6053,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>129.2</v>
+        <v>171.7</v>
       </c>
       <c r="V80" t="n">
         <v>259.43</v>
@@ -6123,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>260.3</v>
+        <v>335</v>
       </c>
       <c r="V81" t="n">
         <v>257.03</v>
@@ -6193,7 +6193,7 @@
         <v>2</v>
       </c>
       <c r="U82" t="n">
-        <v>550</v>
+        <v>641.2</v>
       </c>
       <c r="V82" t="n">
         <v>259.43</v>
@@ -6263,7 +6263,7 @@
         <v>3</v>
       </c>
       <c r="U83" t="n">
-        <v>475.8</v>
+        <v>566.9</v>
       </c>
       <c r="V83" t="n">
         <v>260.63</v>
@@ -6333,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>121.2</v>
+        <v>149.2</v>
       </c>
       <c r="V84" t="n">
         <v>224.85</v>
@@ -6403,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>246</v>
+        <v>274.8</v>
       </c>
       <c r="V85" t="n">
         <v>189.07</v>
@@ -6473,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>104.9</v>
+        <v>144.7</v>
       </c>
       <c r="V86" t="n">
         <v>226.05</v>
@@ -6543,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>163.1</v>
+        <v>206.7</v>
       </c>
       <c r="V87" t="n">
         <v>191.47</v>
@@ -6613,7 +6613,7 @@
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>256.3</v>
+        <v>299.2</v>
       </c>
       <c r="V88" t="n">
         <v>999853.29</v>
@@ -6683,7 +6683,7 @@
         <v>3</v>
       </c>
       <c r="U89" t="n">
-        <v>720.6</v>
+        <v>895</v>
       </c>
       <c r="V89" t="n">
         <v>999992.8100000001</v>
@@ -6753,7 +6753,7 @@
         <v>1</v>
       </c>
       <c r="U90" t="n">
-        <v>118.5</v>
+        <v>162.4</v>
       </c>
       <c r="V90" t="n">
         <v>999960.63</v>
@@ -6823,7 +6823,7 @@
         <v>3</v>
       </c>
       <c r="U91" t="n">
-        <v>454.5</v>
+        <v>571.2</v>
       </c>
       <c r="V91" t="n">
         <v>999960.63</v>
@@ -6893,7 +6893,7 @@
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>120.8</v>
+        <v>128.9</v>
       </c>
       <c r="V92" t="n">
         <v>999924.85</v>
@@ -6963,7 +6963,7 @@
         <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>160.3</v>
+        <v>191</v>
       </c>
       <c r="V93" t="n">
         <v>999923.65</v>
@@ -7033,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>489</v>
+        <v>498.2</v>
       </c>
       <c r="V94" t="n">
         <v>999922.45</v>
@@ -7103,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>157.1</v>
+        <v>194.7</v>
       </c>
       <c r="V95" t="n">
         <v>999924.85</v>
@@ -7173,7 +7173,7 @@
         <v>2</v>
       </c>
       <c r="U96" t="n">
-        <v>627.6</v>
+        <v>692.2</v>
       </c>
       <c r="V96" t="n">
         <v>999924.85</v>
@@ -7243,7 +7243,7 @@
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>103.9</v>
+        <v>107.1</v>
       </c>
       <c r="V97" t="n">
         <v>999959.4300000001</v>
@@ -7313,7 +7313,7 @@
         <v>1</v>
       </c>
       <c r="U98" t="n">
-        <v>142.7</v>
+        <v>142.1</v>
       </c>
       <c r="V98" t="n">
         <v>999958.23</v>
@@ -7383,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="U99" t="n">
-        <v>363.6</v>
+        <v>379.7</v>
       </c>
       <c r="V99" t="n">
         <v>999957.03</v>
@@ -7453,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>90.3</v>
+        <v>87.2</v>
       </c>
       <c r="V100" t="n">
         <v>999960.63</v>
@@ -7523,7 +7523,7 @@
         <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>104.3</v>
+        <v>102.7</v>
       </c>
       <c r="V101" t="n">
         <v>999959.4300000001</v>
@@ -7593,7 +7593,7 @@
         <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>209.3</v>
+        <v>209.6</v>
       </c>
       <c r="V102" t="n">
         <v>999958.23</v>
@@ -7663,7 +7663,7 @@
         <v>3</v>
       </c>
       <c r="U103" t="n">
-        <v>412.2</v>
+        <v>400.3</v>
       </c>
       <c r="V103" t="n">
         <v>999924.85</v>
@@ -7733,7 +7733,7 @@
         <v>3</v>
       </c>
       <c r="U104" t="n">
-        <v>981.5</v>
+        <v>908.5</v>
       </c>
       <c r="V104" t="n">
         <v>999924.85</v>
@@ -7803,7 +7803,7 @@
         <v>4</v>
       </c>
       <c r="U105" t="n">
-        <v>890.2</v>
+        <v>921.5</v>
       </c>
       <c r="V105" t="n">
         <v>999960.63</v>
@@ -7873,7 +7873,7 @@
         <v>1</v>
       </c>
       <c r="U106" t="n">
-        <v>168.7</v>
+        <v>167.7</v>
       </c>
       <c r="V106" t="n">
         <v>999889.0699999999</v>
@@ -7943,7 +7943,7 @@
         <v>75</v>
       </c>
       <c r="U107" t="n">
-        <v>26180.7</v>
+        <v>19735.8</v>
       </c>
       <c r="V107" t="n">
         <v>999781.73</v>
@@ -8013,7 +8013,7 @@
         <v>5</v>
       </c>
       <c r="U108" t="n">
-        <v>1941</v>
+        <v>1718.8</v>
       </c>
       <c r="V108" t="n">
         <v>999813.92</v>
@@ -8083,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="U109" t="n">
-        <v>217.3</v>
+        <v>209.9</v>
       </c>
       <c r="V109" t="n">
         <v>999858.08</v>
@@ -8153,7 +8153,7 @@
         <v>3</v>
       </c>
       <c r="U110" t="n">
-        <v>517.6</v>
+        <v>446</v>
       </c>
       <c r="V110" t="n">
         <v>999992.8100000001</v>
@@ -8223,7 +8223,7 @@
         <v>4</v>
       </c>
       <c r="U111" t="n">
-        <v>1114</v>
+        <v>1071.6</v>
       </c>
       <c r="V111" t="n">
         <v>999992.8100000001</v>
@@ -8293,7 +8293,7 @@
         <v>2</v>
       </c>
       <c r="U112" t="n">
-        <v>263.4</v>
+        <v>256.5</v>
       </c>
       <c r="V112" t="n">
         <v>999960.63</v>
@@ -8363,7 +8363,7 @@
         <v>2</v>
       </c>
       <c r="U113" t="n">
-        <v>525.5</v>
+        <v>486.8</v>
       </c>
       <c r="V113" t="n">
         <v>999960.63</v>
@@ -8433,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="U114" t="n">
-        <v>144.6</v>
+        <v>137.8</v>
       </c>
       <c r="V114" t="n">
         <v>999924.85</v>
@@ -8503,7 +8503,7 @@
         <v>1</v>
       </c>
       <c r="U115" t="n">
-        <v>266.6</v>
+        <v>247.6</v>
       </c>
       <c r="V115" t="n">
         <v>999923.65</v>
@@ -8573,7 +8573,7 @@
         <v>1</v>
       </c>
       <c r="U116" t="n">
-        <v>718.6</v>
+        <v>488.4</v>
       </c>
       <c r="V116" t="n">
         <v>999921.25</v>
@@ -8643,7 +8643,7 @@
         <v>2</v>
       </c>
       <c r="U117" t="n">
-        <v>357.4</v>
+        <v>340.7</v>
       </c>
       <c r="V117" t="n">
         <v>999924.85</v>
@@ -8713,7 +8713,7 @@
         <v>2</v>
       </c>
       <c r="U118" t="n">
-        <v>1029.4</v>
+        <v>869</v>
       </c>
       <c r="V118" t="n">
         <v>999924.85</v>
@@ -8783,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>133.8</v>
+        <v>124.4</v>
       </c>
       <c r="V119" t="n">
         <v>999959.4300000001</v>
@@ -8853,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="U120" t="n">
-        <v>227.9</v>
+        <v>214.5</v>
       </c>
       <c r="V120" t="n">
         <v>999958.23</v>
@@ -8923,7 +8923,7 @@
         <v>1</v>
       </c>
       <c r="U121" t="n">
-        <v>411.1</v>
+        <v>406.1</v>
       </c>
       <c r="V121" t="n">
         <v>999955.84</v>
@@ -8993,7 +8993,7 @@
         <v>1</v>
       </c>
       <c r="U122" t="n">
-        <v>92.3</v>
+        <v>89.5</v>
       </c>
       <c r="V122" t="n">
         <v>999960.63</v>
@@ -9063,7 +9063,7 @@
         <v>1</v>
       </c>
       <c r="U123" t="n">
-        <v>142.7</v>
+        <v>127.8</v>
       </c>
       <c r="V123" t="n">
         <v>999959.4300000001</v>
@@ -9133,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="U124" t="n">
-        <v>291</v>
+        <v>263.5</v>
       </c>
       <c r="V124" t="n">
         <v>999957.03</v>
@@ -9203,7 +9203,7 @@
         <v>2</v>
       </c>
       <c r="U125" t="n">
-        <v>590.2</v>
+        <v>546.7</v>
       </c>
       <c r="V125" t="n">
         <v>999959.4300000001</v>
@@ -9273,7 +9273,7 @@
         <v>3</v>
       </c>
       <c r="U126" t="n">
-        <v>581</v>
+        <v>473.1</v>
       </c>
       <c r="V126" t="n">
         <v>999960.63</v>
@@ -9343,7 +9343,7 @@
         <v>1</v>
       </c>
       <c r="U127" t="n">
-        <v>161.9</v>
+        <v>128.9</v>
       </c>
       <c r="V127" t="n">
         <v>999924.85</v>
@@ -9413,7 +9413,7 @@
         <v>1</v>
       </c>
       <c r="U128" t="n">
-        <v>396.6</v>
+        <v>235.8</v>
       </c>
       <c r="V128" t="n">
         <v>999889.0699999999</v>
@@ -9483,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="U129" t="n">
-        <v>267.2</v>
+        <v>113.9</v>
       </c>
       <c r="V129" t="n">
         <v>999926.05</v>
@@ -9553,7 +9553,7 @@
         <v>1</v>
       </c>
       <c r="U130" t="n">
-        <v>749.1</v>
+        <v>178.6</v>
       </c>
       <c r="V130" t="n">
         <v>999891.47</v>
